--- a/uploads/RepairItems.xlsx
+++ b/uploads/RepairItems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALLAH\Warehouse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B684F6-C9D6-498A-B718-30CAD4744E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EFA1D4-26FE-4AB9-94C4-EF8444927381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" tabRatio="560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="6375" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لیست تعمیرات" sheetId="5" r:id="rId1"/>
@@ -2578,6 +2578,9 @@
     <xf numFmtId="0" fontId="41" fillId="10" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2590,9 +2593,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Good" xfId="4" builtinId="26"/>
@@ -6603,6 +6603,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -6620,16 +6630,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -6647,6 +6647,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -6694,16 +6704,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -6721,6 +6721,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -6768,16 +6778,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -6856,6 +6856,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -6886,16 +6896,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7658,7 +7658,7 @@
       <c r="F1" s="91" t="s">
         <v>559</v>
       </c>
-      <c r="G1" s="96" t="s">
+      <c r="G1" s="92" t="s">
         <v>553</v>
       </c>
     </row>
@@ -7997,14 +7997,14 @@
       <c r="G17" s="27"/>
     </row>
     <row r="18" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="93" t="s">
         <v>237</v>
       </c>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="94"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="95"/>
     </row>
     <row r="19" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="31"/>
@@ -10581,7 +10581,7 @@
       <selection pane="bottomLeft" activeCell="D148" sqref="D148"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-      <autoFilter ref="A2:F111" xr:uid="{978A047A-56C1-4C67-B98D-D82C09E5E865}"/>
+      <autoFilter ref="A2:F111" xr:uid="{A13B5697-0F80-44C4-B29E-A6BDE093E0F6}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="1">
@@ -10716,15 +10716,15 @@
     <cfRule type="duplicateValues" dxfId="439" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103">
-    <cfRule type="duplicateValues" dxfId="438" priority="367"/>
-    <cfRule type="duplicateValues" dxfId="437" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="367"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C104">
     <cfRule type="duplicateValues" dxfId="436" priority="346"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C105">
-    <cfRule type="duplicateValues" dxfId="435" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="334"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C106">
     <cfRule type="duplicateValues" dxfId="433" priority="322"/>
@@ -10758,8 +10758,8 @@
     <cfRule type="duplicateValues" dxfId="421" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C120">
-    <cfRule type="duplicateValues" dxfId="420" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="419" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C121">
     <cfRule type="duplicateValues" dxfId="418" priority="193"/>
@@ -10778,8 +10778,8 @@
     <cfRule type="duplicateValues" dxfId="413" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C132">
-    <cfRule type="duplicateValues" dxfId="412" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="411" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C133">
     <cfRule type="duplicateValues" dxfId="410" priority="100"/>
@@ -10789,8 +10789,8 @@
     <cfRule type="duplicateValues" dxfId="408" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C141">
-    <cfRule type="duplicateValues" dxfId="407" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C142">
     <cfRule type="duplicateValues" dxfId="405" priority="48"/>
@@ -10822,25 +10822,25 @@
   <conditionalFormatting sqref="D34">
     <cfRule type="duplicateValues" dxfId="396" priority="613"/>
     <cfRule type="duplicateValues" dxfId="395" priority="615"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="616"/>
-    <cfRule type="duplicateValues" dxfId="393" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="duplicateValues" dxfId="392" priority="599"/>
-    <cfRule type="duplicateValues" dxfId="391" priority="601"/>
-    <cfRule type="duplicateValues" dxfId="390" priority="602"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="602"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="601"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="duplicateValues" dxfId="389" priority="595"/>
-    <cfRule type="duplicateValues" dxfId="388" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="595"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="duplicateValues" dxfId="387" priority="593"/>
-    <cfRule type="duplicateValues" dxfId="386" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53">
-    <cfRule type="duplicateValues" dxfId="385" priority="590"/>
-    <cfRule type="duplicateValues" dxfId="384" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55">
     <cfRule type="duplicateValues" dxfId="383" priority="588"/>
@@ -10855,16 +10855,16 @@
     <cfRule type="duplicateValues" dxfId="378" priority="584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="duplicateValues" dxfId="377" priority="581"/>
-    <cfRule type="duplicateValues" dxfId="376" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
     <cfRule type="duplicateValues" dxfId="375" priority="578"/>
     <cfRule type="duplicateValues" dxfId="374" priority="579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60">
-    <cfRule type="duplicateValues" dxfId="373" priority="574"/>
-    <cfRule type="duplicateValues" dxfId="372" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D62">
     <cfRule type="duplicateValues" dxfId="371" priority="571"/>
@@ -10881,49 +10881,49 @@
     <cfRule type="duplicateValues" dxfId="364" priority="551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D74">
-    <cfRule type="duplicateValues" dxfId="363" priority="545"/>
-    <cfRule type="duplicateValues" dxfId="362" priority="546"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="547"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="547"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75">
     <cfRule type="duplicateValues" dxfId="360" priority="541"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="542"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="543"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="542"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D76">
-    <cfRule type="duplicateValues" dxfId="356" priority="536"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="537"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="538"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78">
-    <cfRule type="duplicateValues" dxfId="352" priority="530"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="531"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="534"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="530"/>
     <cfRule type="duplicateValues" dxfId="349" priority="533"/>
-    <cfRule type="duplicateValues" dxfId="348" priority="534"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79">
-    <cfRule type="duplicateValues" dxfId="347" priority="524"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="525"/>
-    <cfRule type="duplicateValues" dxfId="345" priority="526"/>
-    <cfRule type="duplicateValues" dxfId="344" priority="527"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D80">
-    <cfRule type="duplicateValues" dxfId="342" priority="518"/>
-    <cfRule type="duplicateValues" dxfId="341" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="521"/>
     <cfRule type="duplicateValues" dxfId="340" priority="520"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="521"/>
-    <cfRule type="duplicateValues" dxfId="338" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81">
-    <cfRule type="duplicateValues" dxfId="337" priority="512"/>
-    <cfRule type="duplicateValues" dxfId="336" priority="513"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="514"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="515"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82">
     <cfRule type="duplicateValues" dxfId="332" priority="508"/>
@@ -10931,38 +10931,38 @@
     <cfRule type="duplicateValues" dxfId="330" priority="510"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83">
-    <cfRule type="duplicateValues" dxfId="329" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="502"/>
-    <cfRule type="duplicateValues" dxfId="326" priority="503"/>
-    <cfRule type="duplicateValues" dxfId="325" priority="504"/>
-    <cfRule type="duplicateValues" dxfId="324" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="500"/>
     <cfRule type="duplicateValues" dxfId="323" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="322" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85">
-    <cfRule type="duplicateValues" dxfId="321" priority="490"/>
-    <cfRule type="duplicateValues" dxfId="320" priority="491"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="495"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="314" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D86">
-    <cfRule type="duplicateValues" dxfId="313" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="479"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="480"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="483"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87">
-    <cfRule type="duplicateValues" dxfId="305" priority="469"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="469"/>
     <cfRule type="duplicateValues" dxfId="303" priority="471"/>
     <cfRule type="duplicateValues" dxfId="302" priority="472"/>
     <cfRule type="duplicateValues" dxfId="301" priority="473"/>
@@ -10971,302 +10971,302 @@
     <cfRule type="duplicateValues" dxfId="298" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D88">
-    <cfRule type="duplicateValues" dxfId="297" priority="460"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="463"/>
     <cfRule type="duplicateValues" dxfId="295" priority="462"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="463"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="464"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="467"/>
     <cfRule type="duplicateValues" dxfId="291" priority="466"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D89">
-    <cfRule type="duplicateValues" dxfId="289" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="288" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="455"/>
     <cfRule type="duplicateValues" dxfId="287" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="459"/>
     <cfRule type="duplicateValues" dxfId="283" priority="458"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="457"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D90">
-    <cfRule type="duplicateValues" dxfId="281" priority="442"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="445"/>
     <cfRule type="duplicateValues" dxfId="279" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="447"/>
     <cfRule type="duplicateValues" dxfId="277" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101">
-    <cfRule type="duplicateValues" dxfId="273" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="399"/>
     <cfRule type="duplicateValues" dxfId="272" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="392"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="393"/>
-    <cfRule type="duplicateValues" dxfId="269" priority="394"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="396"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="397"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="395"/>
     <cfRule type="duplicateValues" dxfId="264" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D102">
-    <cfRule type="duplicateValues" dxfId="263" priority="378"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="380"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="381"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="382"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="383"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="384"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="385"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="386"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="387"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="387"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D103">
-    <cfRule type="duplicateValues" dxfId="253" priority="366"/>
-    <cfRule type="duplicateValues" dxfId="252" priority="368"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="371"/>
     <cfRule type="duplicateValues" dxfId="250" priority="370"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="371"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="372"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="373"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="375"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="375"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D104">
-    <cfRule type="duplicateValues" dxfId="243" priority="345"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="349"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="351"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="duplicateValues" dxfId="233" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="336"/>
     <cfRule type="duplicateValues" dxfId="232" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="336"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="337"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="339"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="340"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D106">
-    <cfRule type="duplicateValues" dxfId="223" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="323"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="325"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="326"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="327"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="328"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="330"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="321"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107">
-    <cfRule type="duplicateValues" dxfId="213" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="304"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="297"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D108">
-    <cfRule type="duplicateValues" dxfId="203" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="288"/>
     <cfRule type="duplicateValues" dxfId="202" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="293"/>
     <cfRule type="duplicateValues" dxfId="197" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="289"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D109">
-    <cfRule type="duplicateValues" dxfId="193" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="277"/>
     <cfRule type="duplicateValues" dxfId="191" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="280"/>
     <cfRule type="duplicateValues" dxfId="185" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="273"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D110">
-    <cfRule type="duplicateValues" dxfId="182" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111">
-    <cfRule type="duplicateValues" dxfId="172" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="255"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D117">
-    <cfRule type="duplicateValues" dxfId="162" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="202"/>
     <cfRule type="duplicateValues" dxfId="161" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D125">
-    <cfRule type="duplicateValues" dxfId="159" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="183"/>
     <cfRule type="duplicateValues" dxfId="155" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="190"/>
     <cfRule type="duplicateValues" dxfId="148" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D126">
-    <cfRule type="duplicateValues" dxfId="146" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="169"/>
     <cfRule type="duplicateValues" dxfId="142" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="175"/>
     <cfRule type="duplicateValues" dxfId="136" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D127">
-    <cfRule type="duplicateValues" dxfId="133" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D128">
-    <cfRule type="duplicateValues" dxfId="121" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="138"/>
     <cfRule type="duplicateValues" dxfId="113" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="150"/>
     <cfRule type="duplicateValues" dxfId="111" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D131">
-    <cfRule type="duplicateValues" dxfId="109" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D132">
-    <cfRule type="duplicateValues" dxfId="97" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="115"/>
     <cfRule type="duplicateValues" dxfId="94" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="121"/>
     <cfRule type="duplicateValues" dxfId="88" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D133">
-    <cfRule type="duplicateValues" dxfId="85" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="109"/>
     <cfRule type="duplicateValues" dxfId="76" priority="107"/>
     <cfRule type="duplicateValues" dxfId="75" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D140">
-    <cfRule type="duplicateValues" dxfId="73" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="57"/>
     <cfRule type="duplicateValues" dxfId="69" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D143:D155">
-    <cfRule type="duplicateValues" dxfId="60" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="34"/>
     <cfRule type="duplicateValues" dxfId="56" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
     <cfRule type="duplicateValues" dxfId="47" priority="633"/>
@@ -11501,7 +11501,7 @@
     <customSheetView guid="{4E9100F2-A511-4BAB-A26D-F817BBFCED8B}" showAutoFilter="1">
       <selection activeCell="E18" sqref="E18"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:I6" xr:uid="{1C183B81-2626-48FB-BC1D-2E1EB4186565}"/>
+      <autoFilter ref="A1:I6" xr:uid="{E251F609-13B3-40DD-866A-6F42315D55CF}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13346,7 +13346,7 @@
       <selection activeCell="H10" sqref="H10"/>
       <pageMargins left="0.25" right="0.25" top="0.43" bottom="0.24" header="0.32" footer="0.18"/>
       <pageSetup paperSize="9" scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
-      <autoFilter ref="A2:S2" xr:uid="{394B12DC-4DAA-418E-AB6E-DED08C311E6E}"/>
+      <autoFilter ref="A2:S2" xr:uid="{A68EA6CE-DC05-487F-ACBF-C0C39C3A248D}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="33" type="noConversion"/>
@@ -13474,66 +13474,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="95"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="95"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="95"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
+      <c r="A4" s="96"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
     </row>
     <row r="5" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="95"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
+      <c r="A5" s="96"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
     </row>
     <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="95"/>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
+      <c r="A6" s="96"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
     </row>
     <row r="7" spans="1:13" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
